--- a/samples/CopilotCheck_demo.xlsx
+++ b/samples/CopilotCheck_demo.xlsx
@@ -51,12 +51,18 @@
     <t>Date d'execution</t>
   </si>
   <si>
-    <t>2026-08-15 12:24:06</t>
+    <t>2026-08-15 13:20:05</t>
   </si>
   <si>
     <t>Duree (secondes)</t>
   </si>
   <si>
+    <t>Langue du rapport</t>
+  </si>
+  <si>
+    <t>FR</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -117,7 +123,7 @@
     <t>Conforme</t>
   </si>
   <si>
-    <t>NonConforme</t>
+    <t>Non conforme</t>
   </si>
   <si>
     <t>Attention</t>
@@ -126,10 +132,10 @@
     <t>Manuel</t>
   </si>
   <si>
-    <t>NonEvalue</t>
-  </si>
-  <si>
-    <t>TauxPourcent</t>
+    <t>Non evalue</t>
+  </si>
+  <si>
+    <t>Taux %</t>
   </si>
   <si>
     <t>Bloquant</t>
@@ -233,9 +239,6 @@
   </si>
   <si>
     <t>SKU Microsoft 365 Copilot acheté et visible sur le tenant</t>
-  </si>
-  <si>
-    <t>Non conforme</t>
   </si>
   <si>
     <t>Ecart constate par rapport a la valeur attendue</t>
@@ -791,9 +794,6 @@
     <t>Configurer le quota OneDrive à 1 To minimum</t>
   </si>
   <si>
-    <t>Non evalue</t>
-  </si>
-  <si>
     <t>Service non connecte lors de cette execution</t>
   </si>
   <si>
@@ -1856,7 +1856,7 @@
     <t>Horodatage</t>
   </si>
   <si>
-    <t>Level</t>
+    <t>Niveau</t>
   </si>
   <si>
     <t>Message</t>
@@ -1865,7 +1865,7 @@
     <t>INFO</t>
   </si>
   <si>
-    <t>Generation de donnees de demonstration (aucun tenant contacte)</t>
+    <t>Donnees de demonstration - langue fr (aucun tenant contacte)</t>
   </si>
 </sst>
 </file>
@@ -1946,36 +1946,36 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ParPriorite" displayName="ParPriorite" ref="A26:I29" headerRowCount="1">
-  <autoFilter ref="A26:I29"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ParPriorite" displayName="ParPriorite" ref="A27:I30" headerRowCount="1">
+  <autoFilter ref="A27:I30"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Priorite"/>
     <tableColumn id="2" name="Total"/>
     <tableColumn id="3" name="Evaluables"/>
     <tableColumn id="4" name="Conforme"/>
-    <tableColumn id="5" name="NonConforme"/>
+    <tableColumn id="5" name="Non conforme"/>
     <tableColumn id="6" name="Attention"/>
     <tableColumn id="7" name="Manuel"/>
-    <tableColumn id="8" name="NonEvalue"/>
-    <tableColumn id="9" name="TauxPourcent"/>
+    <tableColumn id="8" name="Non evalue"/>
+    <tableColumn id="9" name="Taux %"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ParSection" displayName="ParSection" ref="A32:I41" headerRowCount="1">
-  <autoFilter ref="A32:I41"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="ParSection" displayName="ParSection" ref="A33:I42" headerRowCount="1">
+  <autoFilter ref="A33:I42"/>
   <tableColumns count="9">
     <tableColumn id="1" name="Section"/>
     <tableColumn id="2" name="Total"/>
     <tableColumn id="3" name="Evaluables"/>
     <tableColumn id="4" name="Conforme"/>
-    <tableColumn id="5" name="NonConforme"/>
+    <tableColumn id="5" name="Non conforme"/>
     <tableColumn id="6" name="Attention"/>
     <tableColumn id="7" name="Manuel"/>
-    <tableColumn id="8" name="NonEvalue"/>
-    <tableColumn id="9" name="TauxPourcent"/>
+    <tableColumn id="8" name="Non evalue"/>
+    <tableColumn id="9" name="Taux %"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1983,18 +1983,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="42.2984733581543" customWidth="1"/>
     <col min="2" max="2" width="9.140625" customWidth="1"/>
     <col min="3" max="3" width="13.190505027770996" customWidth="1"/>
     <col min="4" max="4" width="12.575643539428711" customWidth="1"/>
-    <col min="5" max="5" width="16.3149471282959" customWidth="1"/>
+    <col min="5" max="5" width="16.563551902770996" customWidth="1"/>
     <col min="6" max="6" width="12.3065767288208" customWidth="1"/>
     <col min="7" max="7" width="10.546904563903809" customWidth="1"/>
-    <col min="8" max="8" width="13.315320014953613" customWidth="1"/>
-    <col min="9" max="9" width="16.075549125671387" customWidth="1"/>
+    <col min="8" max="8" width="13.837081909179688" customWidth="1"/>
+    <col min="9" max="9" width="10.006725788116455" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2047,7 +2047,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="0">
-        <v>1.2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="8">
@@ -2055,103 +2055,103 @@
         <v>12</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="0">
-        <v>59</v>
+        <v>14</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10" s="0">
-        <v>23</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11" s="0">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12" s="0">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B13" s="0">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14" s="0">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="0" t="s">
-        <v>12</v>
+        <v>20</v>
+      </c>
+      <c r="B15" s="0">
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="0">
-        <v>36</v>
+        <v>14</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B17" s="0">
-        <v>63.9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B18" s="0">
-        <v>7</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" s="0" t="s">
-        <v>12</v>
+        <v>23</v>
+      </c>
+      <c r="B19" s="0">
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
@@ -2159,312 +2159,291 @@
         <v>24</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="0" t="s">
         <v>25</v>
-      </c>
-      <c r="B22" s="0" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B26" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="B25" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="B27" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="C27" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="D27" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="E27" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="H26" s="3" t="s">
+      <c r="F27" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="I26" s="3" t="s">
+      <c r="G27" s="3" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="0" t="s">
+      <c r="H27" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="0">
-        <v>24</v>
-      </c>
-      <c r="C27" s="0">
-        <v>19</v>
-      </c>
-      <c r="D27" s="0">
-        <v>10</v>
-      </c>
-      <c r="E27" s="0">
-        <v>7</v>
-      </c>
-      <c r="F27" s="0">
-        <v>2</v>
-      </c>
-      <c r="G27" s="0">
-        <v>3</v>
-      </c>
-      <c r="H27" s="0">
-        <v>2</v>
-      </c>
-      <c r="I27" s="0">
-        <v>52.6</v>
+      <c r="I27" s="3" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B28" s="0">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C28" s="0">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D28" s="0">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E28" s="0">
+        <v>7</v>
+      </c>
+      <c r="F28" s="0">
+        <v>2</v>
+      </c>
+      <c r="G28" s="0">
         <v>3</v>
       </c>
-      <c r="F28" s="0">
-        <v>1</v>
-      </c>
-      <c r="G28" s="0">
-        <v>7</v>
-      </c>
       <c r="H28" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I28" s="0">
-        <v>75</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B29" s="0">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="C29" s="0">
+        <v>16</v>
+      </c>
+      <c r="D29" s="0">
+        <v>12</v>
+      </c>
+      <c r="E29" s="0">
+        <v>3</v>
+      </c>
+      <c r="F29" s="0">
         <v>1</v>
-      </c>
-      <c r="D29" s="0">
-        <v>1</v>
-      </c>
-      <c r="E29" s="0">
-        <v>0</v>
-      </c>
-      <c r="F29" s="0">
-        <v>0</v>
       </c>
       <c r="G29" s="0">
         <v>7</v>
       </c>
       <c r="H29" s="0">
+        <v>3</v>
+      </c>
+      <c r="I29" s="0">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="0">
+        <v>9</v>
+      </c>
+      <c r="C30" s="0">
         <v>1</v>
       </c>
-      <c r="I29" s="0">
+      <c r="D30" s="0">
+        <v>1</v>
+      </c>
+      <c r="E30" s="0">
+        <v>0</v>
+      </c>
+      <c r="F30" s="0">
+        <v>0</v>
+      </c>
+      <c r="G30" s="0">
+        <v>7</v>
+      </c>
+      <c r="H30" s="0">
+        <v>1</v>
+      </c>
+      <c r="I30" s="0">
         <v>100</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D32" s="4" t="s">
+    <row r="33">
+      <c r="A33" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="C33" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="D33" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="E33" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="H32" s="4" t="s">
+      <c r="F33" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="I32" s="4" t="s">
+      <c r="G33" s="4" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="B33" s="0">
-        <v>10</v>
-      </c>
-      <c r="C33" s="0">
-        <v>4</v>
-      </c>
-      <c r="D33" s="0">
-        <v>2</v>
-      </c>
-      <c r="E33" s="0">
-        <v>2</v>
-      </c>
-      <c r="F33" s="0">
-        <v>0</v>
-      </c>
-      <c r="G33" s="0">
-        <v>5</v>
-      </c>
-      <c r="H33" s="0">
-        <v>1</v>
-      </c>
-      <c r="I33" s="0">
-        <v>50</v>
+      <c r="H33" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B34" s="0">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C34" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D34" s="0">
         <v>2</v>
       </c>
       <c r="E34" s="0">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F34" s="0">
         <v>0</v>
       </c>
       <c r="G34" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H34" s="0">
         <v>1</v>
       </c>
       <c r="I34" s="0">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B35" s="0">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C35" s="0">
         <v>2</v>
       </c>
       <c r="D35" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" s="0">
         <v>0</v>
       </c>
       <c r="G35" s="0">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H35" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" s="0">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B36" s="0">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C36" s="0">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D36" s="0">
+        <v>1</v>
+      </c>
+      <c r="E36" s="0">
+        <v>1</v>
+      </c>
+      <c r="F36" s="0">
+        <v>0</v>
+      </c>
+      <c r="G36" s="0">
         <v>2</v>
-      </c>
-      <c r="E36" s="0">
-        <v>0</v>
-      </c>
-      <c r="F36" s="0">
-        <v>1</v>
-      </c>
-      <c r="G36" s="0">
-        <v>0</v>
       </c>
       <c r="H36" s="0">
         <v>0</v>
       </c>
       <c r="I36" s="0">
-        <v>66.7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B37" s="0">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C37" s="0">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D37" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E37" s="0">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F37" s="0">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G37" s="0">
         <v>0</v>
@@ -2478,22 +2457,22 @@
     </row>
     <row r="38">
       <c r="A38" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B38" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C38" s="0">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D38" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E38" s="0">
         <v>2</v>
       </c>
       <c r="F38" s="0">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" s="0">
         <v>0</v>
@@ -2502,24 +2481,24 @@
         <v>0</v>
       </c>
       <c r="I38" s="0">
-        <v>40</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B39" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C39" s="0">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D39" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E39" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" s="0">
         <v>1</v>
@@ -2531,33 +2510,33 @@
         <v>0</v>
       </c>
       <c r="I39" s="0">
-        <v>66.7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B40" s="0">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C40" s="0">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D40" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E40" s="0">
         <v>1</v>
       </c>
       <c r="F40" s="0">
+        <v>1</v>
+      </c>
+      <c r="G40" s="0">
         <v>0</v>
       </c>
-      <c r="G40" s="0">
-        <v>2</v>
-      </c>
       <c r="H40" s="0">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I40" s="0">
         <v>66.7</v>
@@ -2565,16 +2544,16 @@
     </row>
     <row r="41">
       <c r="A41" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B41" s="0">
         <v>8</v>
       </c>
       <c r="C41" s="0">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D41" s="0">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E41" s="0">
         <v>1</v>
@@ -2586,9 +2565,38 @@
         <v>2</v>
       </c>
       <c r="H41" s="0">
+        <v>3</v>
+      </c>
+      <c r="I41" s="0">
+        <v>66.7</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0" t="s">
+        <v>51</v>
+      </c>
+      <c r="B42" s="0">
+        <v>8</v>
+      </c>
+      <c r="C42" s="0">
+        <v>5</v>
+      </c>
+      <c r="D42" s="0">
+        <v>4</v>
+      </c>
+      <c r="E42" s="0">
         <v>1</v>
       </c>
-      <c r="I41" s="0">
+      <c r="F42" s="0">
+        <v>0</v>
+      </c>
+      <c r="G42" s="0">
+        <v>2</v>
+      </c>
+      <c r="H42" s="0">
+        <v>1</v>
+      </c>
+      <c r="I42" s="0">
         <v>80</v>
       </c>
     </row>
@@ -2623,43 +2631,43 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L1" s="8" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2">
@@ -2667,40 +2675,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="L2" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3">
@@ -2708,40 +2716,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F3" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="M3" s="5" t="s">
         <v>70</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="4">
@@ -2749,40 +2757,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5">
@@ -2790,40 +2798,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6">
@@ -2831,40 +2839,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M6" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7">
@@ -2872,40 +2880,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8">
@@ -2913,40 +2921,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M8" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9">
@@ -2954,40 +2962,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10">
@@ -2995,40 +3003,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M10" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11">
@@ -3036,40 +3044,40 @@
         <v>10</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12">
@@ -3077,40 +3085,40 @@
         <v>11</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M12" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -3118,40 +3126,40 @@
         <v>12</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D13" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E13" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="M13" s="5" t="s">
         <v>137</v>
-      </c>
-      <c r="E13" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="F13" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="L13" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="M13" s="5" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="14">
@@ -3159,40 +3167,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M14" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -3200,40 +3208,40 @@
         <v>14</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E15" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F15" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16">
@@ -3241,40 +3249,40 @@
         <v>15</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E16" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="M16" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="17">
@@ -3282,40 +3290,40 @@
         <v>16</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E17" s="0" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18">
@@ -3323,40 +3331,40 @@
         <v>17</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D18" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="E18" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="M18" s="5" t="s">
         <v>167</v>
-      </c>
-      <c r="E18" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="F18" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="K18" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="L18" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="M18" s="5" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="19">
@@ -3364,40 +3372,40 @@
         <v>18</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E19" s="0" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="20">
@@ -3405,40 +3413,40 @@
         <v>19</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E20" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M20" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="21">
@@ -3446,40 +3454,40 @@
         <v>20</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E21" s="0" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M21" s="5" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="22">
@@ -3487,40 +3495,40 @@
         <v>21</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M22" s="5" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="23">
@@ -3528,40 +3536,40 @@
         <v>22</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="M23" s="5" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="24">
@@ -3569,19 +3577,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E24" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>204</v>
+        <v>37</v>
       </c>
       <c r="G24" s="7" t="s">
         <v>205</v>
@@ -3590,7 +3598,7 @@
         <v>206</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J24" s="7" t="s">
         <v>207</v>
@@ -3610,7 +3618,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C25" s="0" t="s">
         <v>211</v>
@@ -3619,13 +3627,13 @@
         <v>212</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H25" s="7" t="s">
         <v>213</v>
@@ -3651,7 +3659,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C26" s="0" t="s">
         <v>211</v>
@@ -3660,19 +3668,19 @@
         <v>219</v>
       </c>
       <c r="E26" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H26" s="7" t="s">
         <v>220</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J26" s="7" t="s">
         <v>221</v>
@@ -3684,7 +3692,7 @@
         <v>223</v>
       </c>
       <c r="M26" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27">
@@ -3692,7 +3700,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C27" s="0" t="s">
         <v>211</v>
@@ -3701,19 +3709,19 @@
         <v>224</v>
       </c>
       <c r="E27" s="0" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H27" s="7" t="s">
         <v>225</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J27" s="7" t="s">
         <v>226</v>
@@ -3733,7 +3741,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C28" s="0" t="s">
         <v>230</v>
@@ -3742,13 +3750,13 @@
         <v>231</v>
       </c>
       <c r="E28" s="0" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F28" s="0" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H28" s="7" t="s">
         <v>232</v>
@@ -3774,7 +3782,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C29" s="0" t="s">
         <v>230</v>
@@ -3783,19 +3791,19 @@
         <v>238</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F29" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>239</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J29" s="7" t="s">
         <v>240</v>
@@ -3815,7 +3823,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C30" s="0" t="s">
         <v>230</v>
@@ -3824,19 +3832,19 @@
         <v>243</v>
       </c>
       <c r="E30" s="0" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H30" s="7" t="s">
         <v>244</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J30" s="7" t="s">
         <v>245</v>
@@ -3856,7 +3864,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C31" s="0" t="s">
         <v>230</v>
@@ -3865,19 +3873,19 @@
         <v>249</v>
       </c>
       <c r="E31" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F31" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H31" s="7" t="s">
         <v>250</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J31" s="7" t="s">
         <v>251</v>
@@ -3897,7 +3905,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C32" s="0" t="s">
         <v>230</v>
@@ -3906,13 +3914,13 @@
         <v>254</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H32" s="7" t="s">
         <v>255</v>
@@ -3938,7 +3946,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C33" s="0" t="s">
         <v>230</v>
@@ -3947,19 +3955,19 @@
         <v>259</v>
       </c>
       <c r="E33" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H33" s="7" t="s">
         <v>260</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J33" s="7" t="s">
         <v>261</v>
@@ -3979,7 +3987,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C34" s="0" t="s">
         <v>264</v>
@@ -3988,19 +3996,19 @@
         <v>265</v>
       </c>
       <c r="E34" s="0" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H34" s="7" t="s">
         <v>266</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J34" s="7" t="s">
         <v>267</v>
@@ -4020,7 +4028,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C35" s="0" t="s">
         <v>264</v>
@@ -4029,19 +4037,19 @@
         <v>271</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F35" s="0" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H35" s="7" t="s">
         <v>272</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J35" s="7" t="s">
         <v>273</v>
@@ -4061,7 +4069,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C36" s="0" t="s">
         <v>264</v>
@@ -4070,19 +4078,19 @@
         <v>276</v>
       </c>
       <c r="E36" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H36" s="7" t="s">
         <v>277</v>
       </c>
       <c r="I36" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J36" s="7" t="s">
         <v>278</v>
@@ -4102,7 +4110,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C37" s="0" t="s">
         <v>264</v>
@@ -4111,19 +4119,19 @@
         <v>282</v>
       </c>
       <c r="E37" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F37" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H37" s="7" t="s">
         <v>283</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J37" s="7" t="s">
         <v>284</v>
@@ -4143,7 +4151,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C38" s="0" t="s">
         <v>264</v>
@@ -4152,10 +4160,10 @@
         <v>288</v>
       </c>
       <c r="E38" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F38" s="0" t="s">
         <v>37</v>
-      </c>
-      <c r="F38" s="0" t="s">
-        <v>204</v>
       </c>
       <c r="G38" s="7" t="s">
         <v>205</v>
@@ -4164,7 +4172,7 @@
         <v>289</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J38" s="7" t="s">
         <v>290</v>
@@ -4184,7 +4192,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C39" s="0" t="s">
         <v>264</v>
@@ -4193,19 +4201,19 @@
         <v>293</v>
       </c>
       <c r="E39" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H39" s="7" t="s">
         <v>294</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J39" s="7" t="s">
         <v>295</v>
@@ -4225,7 +4233,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C40" s="0" t="s">
         <v>264</v>
@@ -4234,19 +4242,19 @@
         <v>299</v>
       </c>
       <c r="E40" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F40" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H40" s="7" t="s">
         <v>300</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J40" s="7" t="s">
         <v>301</v>
@@ -4266,7 +4274,7 @@
         <v>40</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C41" s="0" t="s">
         <v>264</v>
@@ -4275,19 +4283,19 @@
         <v>305</v>
       </c>
       <c r="E41" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F41" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H41" s="7" t="s">
         <v>306</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J41" s="7" t="s">
         <v>307</v>
@@ -4307,7 +4315,7 @@
         <v>41</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C42" s="0" t="s">
         <v>264</v>
@@ -4316,19 +4324,19 @@
         <v>311</v>
       </c>
       <c r="E42" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F42" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H42" s="7" t="s">
         <v>312</v>
       </c>
       <c r="I42" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J42" s="7" t="s">
         <v>313</v>
@@ -4348,7 +4356,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C43" s="0" t="s">
         <v>264</v>
@@ -4357,19 +4365,19 @@
         <v>316</v>
       </c>
       <c r="E43" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F43" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H43" s="7" t="s">
         <v>317</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J43" s="7" t="s">
         <v>318</v>
@@ -4389,7 +4397,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C44" s="0" t="s">
         <v>321</v>
@@ -4398,19 +4406,19 @@
         <v>322</v>
       </c>
       <c r="E44" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F44" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H44" s="7" t="s">
         <v>323</v>
       </c>
       <c r="I44" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J44" s="7" t="s">
         <v>324</v>
@@ -4430,7 +4438,7 @@
         <v>44</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C45" s="0" t="s">
         <v>321</v>
@@ -4439,19 +4447,19 @@
         <v>328</v>
       </c>
       <c r="E45" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H45" s="7" t="s">
         <v>329</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J45" s="7" t="s">
         <v>330</v>
@@ -4471,7 +4479,7 @@
         <v>45</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C46" s="0" t="s">
         <v>321</v>
@@ -4480,19 +4488,19 @@
         <v>332</v>
       </c>
       <c r="E46" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F46" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H46" s="7" t="s">
         <v>333</v>
       </c>
       <c r="I46" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J46" s="7" t="s">
         <v>334</v>
@@ -4512,7 +4520,7 @@
         <v>46</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C47" s="0" t="s">
         <v>321</v>
@@ -4521,19 +4529,19 @@
         <v>337</v>
       </c>
       <c r="E47" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F47" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H47" s="7" t="s">
         <v>338</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J47" s="7" t="s">
         <v>339</v>
@@ -4553,7 +4561,7 @@
         <v>47</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C48" s="0" t="s">
         <v>321</v>
@@ -4562,10 +4570,10 @@
         <v>342</v>
       </c>
       <c r="E48" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F48" s="0" t="s">
-        <v>204</v>
+        <v>37</v>
       </c>
       <c r="G48" s="7" t="s">
         <v>205</v>
@@ -4574,7 +4582,7 @@
         <v>343</v>
       </c>
       <c r="I48" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J48" s="7" t="s">
         <v>344</v>
@@ -4594,7 +4602,7 @@
         <v>48</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C49" s="0" t="s">
         <v>321</v>
@@ -4603,19 +4611,19 @@
         <v>347</v>
       </c>
       <c r="E49" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F49" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H49" s="7" t="s">
         <v>348</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J49" s="7" t="s">
         <v>349</v>
@@ -4635,7 +4643,7 @@
         <v>49</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C50" s="0" t="s">
         <v>321</v>
@@ -4644,19 +4652,19 @@
         <v>352</v>
       </c>
       <c r="E50" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F50" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H50" s="7" t="s">
         <v>353</v>
       </c>
       <c r="I50" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J50" s="7" t="s">
         <v>354</v>
@@ -4676,7 +4684,7 @@
         <v>50</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C51" s="0" t="s">
         <v>321</v>
@@ -4685,19 +4693,19 @@
         <v>357</v>
       </c>
       <c r="E51" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F51" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H51" s="7" t="s">
         <v>358</v>
       </c>
       <c r="I51" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J51" s="7" t="s">
         <v>359</v>
@@ -4717,7 +4725,7 @@
         <v>51</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C52" s="0" t="s">
         <v>321</v>
@@ -4726,19 +4734,19 @@
         <v>362</v>
       </c>
       <c r="E52" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F52" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H52" s="7" t="s">
         <v>363</v>
       </c>
       <c r="I52" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J52" s="7" t="s">
         <v>364</v>
@@ -4758,7 +4766,7 @@
         <v>52</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C53" s="0" t="s">
         <v>367</v>
@@ -4767,13 +4775,13 @@
         <v>368</v>
       </c>
       <c r="E53" s="0" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F53" s="0" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H53" s="7" t="s">
         <v>369</v>
@@ -4799,7 +4807,7 @@
         <v>53</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C54" s="0" t="s">
         <v>367</v>
@@ -4808,19 +4816,19 @@
         <v>375</v>
       </c>
       <c r="E54" s="0" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G54" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H54" s="7" t="s">
         <v>376</v>
       </c>
       <c r="I54" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J54" s="7" t="s">
         <v>377</v>
@@ -4840,7 +4848,7 @@
         <v>54</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C55" s="0" t="s">
         <v>367</v>
@@ -4849,19 +4857,19 @@
         <v>380</v>
       </c>
       <c r="E55" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F55" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H55" s="7" t="s">
         <v>381</v>
       </c>
       <c r="I55" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J55" s="7" t="s">
         <v>382</v>
@@ -4881,7 +4889,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C56" s="0" t="s">
         <v>367</v>
@@ -4890,10 +4898,10 @@
         <v>385</v>
       </c>
       <c r="E56" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="F56" s="0" t="s">
         <v>37</v>
-      </c>
-      <c r="F56" s="0" t="s">
-        <v>204</v>
       </c>
       <c r="G56" s="7" t="s">
         <v>205</v>
@@ -4902,7 +4910,7 @@
         <v>386</v>
       </c>
       <c r="I56" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J56" s="7" t="s">
         <v>387</v>
@@ -4922,7 +4930,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C57" s="0" t="s">
         <v>367</v>
@@ -4931,10 +4939,10 @@
         <v>391</v>
       </c>
       <c r="E57" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F57" s="0" t="s">
-        <v>204</v>
+        <v>37</v>
       </c>
       <c r="G57" s="7" t="s">
         <v>205</v>
@@ -4943,7 +4951,7 @@
         <v>392</v>
       </c>
       <c r="I57" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J57" s="7" t="s">
         <v>393</v>
@@ -4963,7 +4971,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C58" s="0" t="s">
         <v>367</v>
@@ -4972,10 +4980,10 @@
         <v>396</v>
       </c>
       <c r="E58" s="0" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>204</v>
+        <v>37</v>
       </c>
       <c r="G58" s="7" t="s">
         <v>205</v>
@@ -4984,7 +4992,7 @@
         <v>397</v>
       </c>
       <c r="I58" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J58" s="7" t="s">
         <v>398</v>
@@ -5004,7 +5012,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C59" s="0" t="s">
         <v>367</v>
@@ -5013,19 +5021,19 @@
         <v>401</v>
       </c>
       <c r="E59" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F59" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H59" s="7" t="s">
         <v>402</v>
       </c>
       <c r="I59" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J59" s="7" t="s">
         <v>403</v>
@@ -5045,7 +5053,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C60" s="0" t="s">
         <v>367</v>
@@ -5054,19 +5062,19 @@
         <v>406</v>
       </c>
       <c r="E60" s="0" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F60" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H60" s="7" t="s">
         <v>407</v>
       </c>
       <c r="I60" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J60" s="7" t="s">
         <v>408</v>
@@ -5078,7 +5086,7 @@
         <v>410</v>
       </c>
       <c r="M60" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -5179,16 +5187,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>411</v>
@@ -5199,13 +5207,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E2" s="0" t="s">
         <v>412</v>
@@ -5216,13 +5224,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="E3" s="0" t="s">
         <v>413</v>
@@ -5233,13 +5241,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E4" s="0" t="s">
         <v>414</v>
@@ -5250,13 +5258,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E5" s="0" t="s">
         <v>415</v>
@@ -5267,13 +5275,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="E6" s="0" t="s">
         <v>416</v>
@@ -5284,13 +5292,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E7" s="0" t="s">
         <v>417</v>
@@ -5301,13 +5309,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="E8" s="0" t="s">
         <v>418</v>
@@ -5318,13 +5326,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E9" s="0" t="s">
         <v>419</v>
@@ -5335,13 +5343,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E10" s="0" t="s">
         <v>420</v>
@@ -5352,13 +5360,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="E11" s="0" t="s">
         <v>421</v>
@@ -5369,13 +5377,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="E12" s="0" t="s">
         <v>422</v>
@@ -5386,13 +5394,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E13" s="0" t="s">
         <v>423</v>
@@ -5403,13 +5411,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E14" s="0" t="s">
         <v>424</v>
@@ -5420,13 +5428,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E15" s="0" t="s">
         <v>425</v>
@@ -5437,13 +5445,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E16" s="0" t="s">
         <v>426</v>
@@ -5454,13 +5462,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E17" s="0" t="s">
         <v>427</v>
@@ -5471,13 +5479,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E18" s="0" t="s">
         <v>428</v>
@@ -5488,13 +5496,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E19" s="0" t="s">
         <v>429</v>
@@ -5505,13 +5513,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="0" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E20" s="0" t="s">
         <v>430</v>
@@ -5522,13 +5530,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="0" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E21" s="0" t="s">
         <v>431</v>
@@ -5539,13 +5547,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E22" s="0" t="s">
         <v>432</v>
@@ -5556,13 +5564,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="E23" s="0" t="s">
         <v>433</v>
@@ -5573,13 +5581,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>204</v>
+        <v>37</v>
       </c>
       <c r="E24" s="0" t="s">
         <v>434</v>
@@ -5590,13 +5598,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C25" s="0" t="s">
         <v>212</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E25" s="0" t="s">
         <v>435</v>
@@ -5607,13 +5615,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C26" s="0" t="s">
         <v>219</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E26" s="0" t="s">
         <v>436</v>
@@ -5624,13 +5632,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C27" s="0" t="s">
         <v>224</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E27" s="0" t="s">
         <v>437</v>
@@ -5641,13 +5649,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C28" s="0" t="s">
         <v>231</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="E28" s="0" t="s">
         <v>438</v>
@@ -5658,13 +5666,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C29" s="0" t="s">
         <v>238</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E29" s="0" t="s">
         <v>439</v>
@@ -5675,13 +5683,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="0" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C30" s="0" t="s">
         <v>243</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E30" s="0" t="s">
         <v>440</v>
@@ -5692,13 +5700,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C31" s="0" t="s">
         <v>249</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E31" s="0" t="s">
         <v>441</v>
@@ -5709,13 +5717,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="0" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C32" s="0" t="s">
         <v>254</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E32" s="0" t="s">
         <v>442</v>
@@ -5726,13 +5734,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C33" s="0" t="s">
         <v>259</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E33" s="0" t="s">
         <v>443</v>
@@ -5743,13 +5751,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C34" s="0" t="s">
         <v>265</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E34" s="0" t="s">
         <v>444</v>
@@ -5760,13 +5768,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C35" s="0" t="s">
         <v>271</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="E35" s="0" t="s">
         <v>445</v>
@@ -5777,13 +5785,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C36" s="0" t="s">
         <v>276</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E36" s="0" t="s">
         <v>446</v>
@@ -5794,13 +5802,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C37" s="0" t="s">
         <v>282</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E37" s="0" t="s">
         <v>447</v>
@@ -5811,13 +5819,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C38" s="0" t="s">
         <v>288</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>204</v>
+        <v>37</v>
       </c>
       <c r="E38" s="0" t="s">
         <v>448</v>
@@ -5828,13 +5836,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C39" s="0" t="s">
         <v>293</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="E39" s="0" t="s">
         <v>449</v>
@@ -5845,13 +5853,13 @@
         <v>39</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C40" s="0" t="s">
         <v>299</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E40" s="0" t="s">
         <v>450</v>
@@ -5862,13 +5870,13 @@
         <v>40</v>
       </c>
       <c r="B41" s="0" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C41" s="0" t="s">
         <v>305</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E41" s="0" t="s">
         <v>451</v>
@@ -5879,13 +5887,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C42" s="0" t="s">
         <v>311</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E42" s="0" t="s">
         <v>452</v>
@@ -5896,13 +5904,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="0" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C43" s="0" t="s">
         <v>316</v>
       </c>
       <c r="D43" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E43" s="0" t="s">
         <v>453</v>
@@ -5913,13 +5921,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C44" s="0" t="s">
         <v>322</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E44" s="0" t="s">
         <v>454</v>
@@ -5930,13 +5938,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C45" s="0" t="s">
         <v>328</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E45" s="0" t="s">
         <v>455</v>
@@ -5947,13 +5955,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C46" s="0" t="s">
         <v>332</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E46" s="0" t="s">
         <v>456</v>
@@ -5964,13 +5972,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="0" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C47" s="0" t="s">
         <v>337</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E47" s="0" t="s">
         <v>457</v>
@@ -5981,13 +5989,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C48" s="0" t="s">
         <v>342</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>204</v>
+        <v>37</v>
       </c>
       <c r="E48" s="0" t="s">
         <v>458</v>
@@ -5998,13 +6006,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="0" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C49" s="0" t="s">
         <v>347</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E49" s="0" t="s">
         <v>459</v>
@@ -6015,13 +6023,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C50" s="0" t="s">
         <v>352</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E50" s="0" t="s">
         <v>460</v>
@@ -6032,13 +6040,13 @@
         <v>50</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C51" s="0" t="s">
         <v>357</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E51" s="0" t="s">
         <v>461</v>
@@ -6049,13 +6057,13 @@
         <v>51</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C52" s="0" t="s">
         <v>362</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E52" s="0" t="s">
         <v>462</v>
@@ -6066,13 +6074,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C53" s="0" t="s">
         <v>368</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="E53" s="0" t="s">
         <v>463</v>
@@ -6083,13 +6091,13 @@
         <v>53</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C54" s="0" t="s">
         <v>375</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E54" s="0" t="s">
         <v>464</v>
@@ -6100,13 +6108,13 @@
         <v>54</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C55" s="0" t="s">
         <v>380</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E55" s="0" t="s">
         <v>465</v>
@@ -6117,13 +6125,13 @@
         <v>55</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C56" s="0" t="s">
         <v>385</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>204</v>
+        <v>37</v>
       </c>
       <c r="E56" s="0" t="s">
         <v>466</v>
@@ -6134,13 +6142,13 @@
         <v>56</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C57" s="0" t="s">
         <v>391</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>204</v>
+        <v>37</v>
       </c>
       <c r="E57" s="0" t="s">
         <v>467</v>
@@ -6151,13 +6159,13 @@
         <v>57</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C58" s="0" t="s">
         <v>396</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>204</v>
+        <v>37</v>
       </c>
       <c r="E58" s="0" t="s">
         <v>468</v>
@@ -6168,13 +6176,13 @@
         <v>58</v>
       </c>
       <c r="B59" s="0" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C59" s="0" t="s">
         <v>401</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E59" s="0" t="s">
         <v>469</v>
@@ -6185,13 +6193,13 @@
         <v>59</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C60" s="0" t="s">
         <v>406</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E60" s="0" t="s">
         <v>470</v>
@@ -6210,7 +6218,7 @@
   <cols>
     <col min="1" max="1" width="19.687713623046875" customWidth="1"/>
     <col min="2" max="2" width="9.140625" customWidth="1"/>
-    <col min="3" max="3" width="59.866554260253906" customWidth="1"/>
+    <col min="3" max="3" width="56.379947662353516" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/samples/CopilotCheck_demo.xlsx
+++ b/samples/CopilotCheck_demo.xlsx
@@ -51,7 +51,7 @@
     <t>Date d'execution</t>
   </si>
   <si>
-    <t>2026-08-15 13:20:05</t>
+    <t>2026-08-15 13:54:24</t>
   </si>
   <si>
     <t>Duree (secondes)</t>

--- a/samples/CopilotCheck_demo.xlsx
+++ b/samples/CopilotCheck_demo.xlsx
@@ -51,7 +51,7 @@
     <t>Date d'execution</t>
   </si>
   <si>
-    <t>2026-08-15 22:04:02</t>
+    <t>2026-08-16 11:58:34</t>
   </si>
   <si>
     <t>Duree (secondes)</t>
@@ -3188,7 +3188,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="0">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="8">

--- a/samples/CopilotCheck_demo.xlsx
+++ b/samples/CopilotCheck_demo.xlsx
@@ -51,7 +51,7 @@
     <t>Date d'execution</t>
   </si>
   <si>
-    <t>2026-08-16 11:58:34</t>
+    <t>2026-08-16 12:11:33</t>
   </si>
   <si>
     <t>Duree (secondes)</t>
@@ -3188,7 +3188,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="0">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="8">

--- a/samples/CopilotCheck_demo.xlsx
+++ b/samples/CopilotCheck_demo.xlsx
@@ -51,7 +51,7 @@
     <t>Date d'execution</t>
   </si>
   <si>
-    <t>2026-08-16 12:11:33</t>
+    <t>2026-08-16 14:35:59</t>
   </si>
   <si>
     <t>Duree (secondes)</t>
@@ -3188,7 +3188,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="0">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="8">

--- a/samples/CopilotCheck_demo.xlsx
+++ b/samples/CopilotCheck_demo.xlsx
@@ -2860,7 +2860,7 @@
     <t>Message</t>
   </si>
   <si>
-    <t>14:57:37</t>
+    <t>15:08:50</t>
   </si>
   <si>
     <t>INFO</t>
@@ -2872,7 +2872,7 @@
     <t>Microsoft 365 Copilot - Etat de configuration du tenant</t>
   </si>
   <si>
-    <t xml:space="preserve">Contoso Demo  ·  00000000-1111-2222-3333-444444444444  ·  genere le 16-08-2026 14:57  ·  FR</t>
+    <t xml:space="preserve">Contoso Demo  ·  00000000-1111-2222-3333-444444444444  ·  genere le 16-08-2026 15:08  ·  FR</t>
   </si>
   <si>
     <t>65 %</t>
@@ -3418,7 +3418,7 @@
     </xdr:to>
     <graphicFrame xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="0" name="Chartz3ktsq"/>
+        <xdr:cNvPr id="0" name="Chart0yuivy"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
